--- a/Excel/03Lecture_Logical_Formulas.xlsx
+++ b/Excel/03Lecture_Logical_Formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chetan Sharma\Desktop\ASDC\FOI_4\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4EC8E3-DCE9-4A04-9C1D-9794A7A0C421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2439C7D3-501B-47B0-B04C-12675AD589A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Student_Result_IF" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="61">
   <si>
     <t>Roll No</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>Rohan</t>
+  </si>
+  <si>
+    <t>Not</t>
   </si>
 </sst>
 </file>
@@ -648,18 +651,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -667,13 +675,13 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>78</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2" s="1" t="str">
         <f>IF(C2&gt;=40,"Pass", "Fail")</f>
         <v>Pass</v>
       </c>
@@ -682,13 +690,13 @@
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>35</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3" s="1" t="str">
         <f t="shared" ref="D3:D7" si="0">IF(C3&gt;=40,"Pass", "Fail")</f>
         <v>Fail</v>
       </c>
@@ -704,13 +712,13 @@
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>62</v>
       </c>
-      <c r="D4" t="str">
+      <c r="D4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Pass</v>
       </c>
@@ -724,13 +732,13 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>40</v>
       </c>
-      <c r="D5" t="str">
+      <c r="D5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Pass</v>
       </c>
@@ -744,13 +752,13 @@
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>28</v>
       </c>
-      <c r="D6" t="str">
+      <c r="D6" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Fail</v>
       </c>
@@ -764,13 +772,13 @@
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>85</v>
       </c>
-      <c r="D7" t="str">
+      <c r="D7" s="1" t="str">
         <f t="shared" si="0"/>
         <v>Pass</v>
       </c>
@@ -787,6 +795,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -1420,6 +1433,9 @@
       <c r="C1" t="s">
         <v>31</v>
       </c>
+      <c r="D1" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -1429,7 +1445,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="str">
-        <f>IF(NOT(B2), "Absent", "Present")</f>
+        <f>IF(B2,"Present","Absent")</f>
+        <v>Present</v>
+      </c>
+      <c r="D2" t="str">
+        <f>IF(NOT(B2),"Absent", "Present")</f>
+        <v>Present</v>
+      </c>
+      <c r="E2" t="b">
+        <f>NOT(B2)</f>
+        <v>0</v>
+      </c>
+      <c r="F2" t="str">
+        <f>IF(E2,"Absent","Present")</f>
         <v>Present</v>
       </c>
     </row>
@@ -1441,7 +1469,19 @@
         <v>0</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" ref="C3:C6" si="0">IF(NOT(B3), "Absent", "Present")</f>
+        <f t="shared" ref="C3:C6" si="0">IF(B3,"Present","Absent")</f>
+        <v>Absent</v>
+      </c>
+      <c r="D3" t="str">
+        <f t="shared" ref="D3:D6" si="1">IF(NOT(B3),"Absent", "Present")</f>
+        <v>Absent</v>
+      </c>
+      <c r="E3" t="b">
+        <f t="shared" ref="E3:E6" si="2">NOT(B3)</f>
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F6" si="3">IF(E3,"Absent","Present")</f>
         <v>Absent</v>
       </c>
     </row>
@@ -1454,6 +1494,18 @@
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
+        <v>Present</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" si="1"/>
+        <v>Present</v>
+      </c>
+      <c r="E4" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="3"/>
         <v>Present</v>
       </c>
       <c r="J4" s="5" t="s">
@@ -1473,6 +1525,18 @@
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
+        <v>Absent</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="1"/>
+        <v>Absent</v>
+      </c>
+      <c r="E5" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="3"/>
         <v>Absent</v>
       </c>
       <c r="J5" s="5"/>
@@ -1490,6 +1554,18 @@
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
+        <v>Present</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="1"/>
+        <v>Present</v>
+      </c>
+      <c r="E6" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="3"/>
         <v>Present</v>
       </c>
       <c r="J6" s="5"/>

--- a/Excel/03Lecture_Logical_Formulas.xlsx
+++ b/Excel/03Lecture_Logical_Formulas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chetan Sharma\Desktop\ASDC\FOI_4\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2439C7D3-501B-47B0-B04C-12675AD589A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{167660E5-B5E9-48FE-A34A-2D9BC68AF972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Student_Result_IF" sheetId="1" r:id="rId1"/>
@@ -823,6 +823,10 @@
         <f>IF(B2&gt;=75,"A",IF(B2&gt;=60,"B",IF(B2&gt;=40,"C","Fail")))</f>
         <v>A</v>
       </c>
+      <c r="D2" t="str">
+        <f>IF(B2&lt;=60, B2+5, "Pass")</f>
+        <v>Pass</v>
+      </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -835,6 +839,10 @@
         <f t="shared" ref="C3:C6" si="0">IF(B3&gt;=75,"A",IF(B3&gt;=60,"B",IF(B3&gt;=40,"C","Fail")))</f>
         <v>C</v>
       </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D6" si="1">IF(B3&lt;=60, B3+5, "Pass")</f>
+        <v>60</v>
+      </c>
     </row>
     <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -846,6 +854,10 @@
       <c r="C4" t="str">
         <f t="shared" si="0"/>
         <v>B</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>44</v>
@@ -865,6 +877,10 @@
       <c r="C5" t="str">
         <f t="shared" si="0"/>
         <v>C</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>47</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
@@ -882,6 +898,10 @@
       <c r="C6" t="str">
         <f t="shared" si="0"/>
         <v>Fail</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
